--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>24.75199818611145</v>
+        <v>25.04640007019043</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>25.04640007019043</v>
+        <v>25.414369106292725</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>25.414369106292725</v>
+        <v>24.65464997291565</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>24.65464997291565</v>
+        <v>24.716322898864746</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>24.716322898864746</v>
+        <v>11.316809892654419</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>11.316809892654419</v>
+        <v>11.961014986038208</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -495,22 +495,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.6210601318510888</v>
+        <v>0.6210589406753743</v>
       </c>
       <c r="C2">
-        <v>0.07216358451678638</v>
+        <v>0.07216355851168951</v>
       </c>
       <c r="D2">
-        <v>8.606281630960563</v>
+        <v>8.606268225738496</v>
       </c>
       <c r="E2">
         <v>0.0</v>
       </c>
       <c r="F2">
-        <v>0.08076358132979498</v>
+        <v>0.08076360476412685</v>
       </c>
       <c r="G2">
-        <v>7.689853788367972</v>
+        <v>7.689836808166256</v>
       </c>
       <c r="H2">
         <v>1.4654943925052066e-14</v>
@@ -521,22 +521,22 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-2.9352724379050628</v>
+        <v>-2.9352709156921564</v>
       </c>
       <c r="C3">
-        <v>0.08431665609374765</v>
+        <v>0.08431647004209687</v>
       </c>
       <c r="D3">
-        <v>-34.81248633296693</v>
+        <v>-34.81254509619126</v>
       </c>
       <c r="E3">
         <v>0.0</v>
       </c>
       <c r="F3">
-        <v>0.09068164912755641</v>
+        <v>0.09068147205877282</v>
       </c>
       <c r="G3">
-        <v>-32.368979458856025</v>
+        <v>-32.369025877631735</v>
       </c>
       <c r="H3">
         <v>0.0</v>
@@ -547,25 +547,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-1.0381291730892686</v>
+        <v>-1.0381340673635875</v>
       </c>
       <c r="C4">
-        <v>0.13411207035114656</v>
+        <v>0.1341131138109748</v>
       </c>
       <c r="D4">
-        <v>-7.740758683175406</v>
+        <v>-7.740734950250887</v>
       </c>
       <c r="E4">
         <v>9.992007221626409e-15</v>
       </c>
       <c r="F4">
-        <v>0.16872231119544776</v>
+        <v>0.16872393982717382</v>
       </c>
       <c r="G4">
-        <v>-6.152886157934979</v>
+        <v>-6.152855773916624</v>
       </c>
       <c r="H4">
-        <v>7.608542684778286e-10</v>
+        <v>7.610001517832643e-10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -573,22 +573,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-1.9838106949069947</v>
+        <v>-1.9838091383948417</v>
       </c>
       <c r="C5">
-        <v>0.08977363024173327</v>
+        <v>0.0897733677176422</v>
       </c>
       <c r="D5">
-        <v>-22.097922180101126</v>
+        <v>-22.097969462774035</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.11722008640368263</v>
+        <v>0.1172198748988496</v>
       </c>
       <c r="G5">
-        <v>-16.923811914582163</v>
+        <v>-16.9238291723711</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -599,22 +599,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.8121119012973305</v>
+        <v>0.8121119237347</v>
       </c>
       <c r="C6">
-        <v>0.09510696951853263</v>
+        <v>0.09510658869847645</v>
       </c>
       <c r="D6">
-        <v>8.538931535812226</v>
+        <v>8.538965962804106</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.09742788268035105</v>
+        <v>0.09742709656905321</v>
       </c>
       <c r="G6">
-        <v>8.33551832345336</v>
+        <v>8.335585810658959</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -625,22 +625,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.8098789078609574</v>
+        <v>0.8098767372652781</v>
       </c>
       <c r="C7">
-        <v>0.10754565415002579</v>
+        <v>0.10754527970723482</v>
       </c>
       <c r="D7">
-        <v>7.530559131019644</v>
+        <v>7.530565167248301</v>
       </c>
       <c r="E7">
         <v>5.062616992290714e-14</v>
       </c>
       <c r="F7">
-        <v>0.11201091045796822</v>
+        <v>0.11201036793057052</v>
       </c>
       <c r="G7">
-        <v>7.230357333492635</v>
+        <v>7.230372975538113</v>
       </c>
       <c r="H7">
         <v>4.816147480823929e-13</v>
@@ -651,22 +651,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.987712419305636</v>
+        <v>0.9877155032883523</v>
       </c>
       <c r="C8">
-        <v>0.0920904098505574</v>
+        <v>0.09209093424281502</v>
       </c>
       <c r="D8">
-        <v>10.725464474623116</v>
+        <v>10.72543688919536</v>
       </c>
       <c r="E8">
         <v>0.0</v>
       </c>
       <c r="F8">
-        <v>0.08969632869233035</v>
+        <v>0.08969709792855984</v>
       </c>
       <c r="G8">
-        <v>11.011737422315393</v>
+        <v>11.011677368592553</v>
       </c>
       <c r="H8">
         <v>0.0</v>
@@ -677,22 +677,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0.468595658699975</v>
+        <v>0.4685934149254077</v>
       </c>
       <c r="C9">
-        <v>0.07064029777442896</v>
+        <v>0.07064033808393454</v>
       </c>
       <c r="D9">
-        <v>6.633545914490775</v>
+        <v>6.633510365828474</v>
       </c>
       <c r="E9">
-        <v>3.2771785285490296e-11</v>
+        <v>3.277955684666267e-11</v>
       </c>
       <c r="F9">
-        <v>0.06126611520519358</v>
+        <v>0.061266119422224194</v>
       </c>
       <c r="G9">
-        <v>7.648528997318436</v>
+        <v>7.648491847443926</v>
       </c>
       <c r="H9">
         <v>2.042810365310288e-14</v>
@@ -713,7 +713,7 @@
         <v>16</v>
       </c>
       <c r="B1">
-        <v>-1444.5644252263073</v>
+        <v>-1444.564425229936</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -729,7 +729,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>11.961014986038208</v>
+        <v>12.317082166671753</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -777,7 +777,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>2905.1288504526146</v>
+        <v>2905.128850459872</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -785,7 +785,7 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>2954.3946897882906</v>
+        <v>2954.394689795548</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -793,7 +793,7 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.40318845002330084</v>
+        <v>0.4031884500218017</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>12.317082166671753</v>
+        <v>12.831422090530396</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>12.831422090530396</v>
+        <v>9.458817958831787</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -495,22 +495,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.6210589406753743</v>
+        <v>0.6210603432321897</v>
       </c>
       <c r="C2">
-        <v>0.07216355851168951</v>
+        <v>0.07216353386437108</v>
       </c>
       <c r="D2">
-        <v>8.606268225738496</v>
+        <v>8.606290601004265</v>
       </c>
       <c r="E2">
         <v>0.0</v>
       </c>
       <c r="F2">
-        <v>0.08076360476412685</v>
+        <v>0.08076355020774202</v>
       </c>
       <c r="G2">
-        <v>7.689836808166256</v>
+        <v>7.689859368919306</v>
       </c>
       <c r="H2">
         <v>1.4654943925052066e-14</v>
@@ -521,22 +521,22 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-2.9352709156921564</v>
+        <v>-2.9352722367064845</v>
       </c>
       <c r="C3">
-        <v>0.08431647004209687</v>
+        <v>0.08431663236081081</v>
       </c>
       <c r="D3">
-        <v>-34.81254509619126</v>
+        <v>-34.81249374554904</v>
       </c>
       <c r="E3">
         <v>0.0</v>
       </c>
       <c r="F3">
-        <v>0.09068147205877282</v>
+        <v>0.09068162916652442</v>
       </c>
       <c r="G3">
-        <v>-32.369025877631735</v>
+        <v>-32.36898436524842</v>
       </c>
       <c r="H3">
         <v>0.0</v>
@@ -547,25 +547,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-1.0381340673635875</v>
+        <v>-1.0381289753399516</v>
       </c>
       <c r="C4">
-        <v>0.1341131138109748</v>
+        <v>0.1341120478157573</v>
       </c>
       <c r="D4">
-        <v>-7.740734950250887</v>
+        <v>-7.740758509378142</v>
       </c>
       <c r="E4">
         <v>9.992007221626409e-15</v>
       </c>
       <c r="F4">
-        <v>0.16872393982717382</v>
+        <v>0.16872227650665184</v>
       </c>
       <c r="G4">
-        <v>-6.152855773916624</v>
+        <v>-6.152886250909634</v>
       </c>
       <c r="H4">
-        <v>7.610001517832643e-10</v>
+        <v>7.608538243886187e-10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -573,22 +573,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-1.9838091383948417</v>
+        <v>-1.983810624459223</v>
       </c>
       <c r="C5">
-        <v>0.0897733677176422</v>
+        <v>0.08977361437416424</v>
       </c>
       <c r="D5">
-        <v>-22.097969462774035</v>
+        <v>-22.097925301202306</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.1172198748988496</v>
+        <v>0.11722004546604478</v>
       </c>
       <c r="G5">
-        <v>-16.9238291723711</v>
+        <v>-16.923817224024837</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -599,22 +599,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.8121119237347</v>
+        <v>0.8121109971613973</v>
       </c>
       <c r="C6">
-        <v>0.09510658869847645</v>
+        <v>0.09510660178405497</v>
       </c>
       <c r="D6">
-        <v>8.538965962804106</v>
+        <v>8.538955045469317</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.09742709656905321</v>
+        <v>0.09742719980278218</v>
       </c>
       <c r="G6">
-        <v>8.335585810658959</v>
+        <v>8.335567467866467</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -625,22 +625,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.8098767372652781</v>
+        <v>0.8098786901129168</v>
       </c>
       <c r="C7">
-        <v>0.10754527970723482</v>
+        <v>0.10754551860020954</v>
       </c>
       <c r="D7">
-        <v>7.530565167248301</v>
+        <v>7.530566597791633</v>
       </c>
       <c r="E7">
         <v>5.062616992290714e-14</v>
       </c>
       <c r="F7">
-        <v>0.11201036793057052</v>
+        <v>0.11201067764352933</v>
       </c>
       <c r="G7">
-        <v>7.230372975538113</v>
+        <v>7.230370417812593</v>
       </c>
       <c r="H7">
         <v>4.816147480823929e-13</v>
@@ -651,22 +651,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.9877155032883523</v>
+        <v>0.9877123870805845</v>
       </c>
       <c r="C8">
-        <v>0.09209093424281502</v>
+        <v>0.0920902875013145</v>
       </c>
       <c r="D8">
-        <v>10.72543688919536</v>
+        <v>10.725478374323524</v>
       </c>
       <c r="E8">
         <v>0.0</v>
       </c>
       <c r="F8">
-        <v>0.08969709792855984</v>
+        <v>0.08969610991637915</v>
       </c>
       <c r="G8">
-        <v>11.011677368592553</v>
+        <v>11.011763921550195</v>
       </c>
       <c r="H8">
         <v>0.0</v>
@@ -677,22 +677,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0.4685934149254077</v>
+        <v>0.46859587521562457</v>
       </c>
       <c r="C9">
-        <v>0.07064033808393454</v>
+        <v>0.07064019073070321</v>
       </c>
       <c r="D9">
-        <v>6.633510365828474</v>
+        <v>6.633559031600307</v>
       </c>
       <c r="E9">
-        <v>3.277955684666267e-11</v>
+        <v>3.2768676661021345e-11</v>
       </c>
       <c r="F9">
-        <v>0.061266119422224194</v>
+        <v>0.061265948703940434</v>
       </c>
       <c r="G9">
-        <v>7.648491847443926</v>
+        <v>7.648553317603094</v>
       </c>
       <c r="H9">
         <v>2.042810365310288e-14</v>
@@ -713,7 +713,7 @@
         <v>16</v>
       </c>
       <c r="B1">
-        <v>-1444.564425229936</v>
+        <v>-1444.5644252262896</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>9.458817958831787</v>
+        <v>7.4570910930633545</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -777,7 +777,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>2905.128850459872</v>
+        <v>2905.128850452579</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -785,7 +785,7 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>2954.394689795548</v>
+        <v>2954.394689788255</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -793,7 +793,7 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.4031884500218017</v>
+        <v>0.40318845002330816</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -495,25 +495,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.6210603432321897</v>
+        <v>0.6277724042767787</v>
       </c>
       <c r="C2">
-        <v>0.07216353386437108</v>
+        <v>0.07328241047093938</v>
       </c>
       <c r="D2">
-        <v>8.606290601004265</v>
+        <v>8.566481373121945</v>
       </c>
       <c r="E2">
         <v>0.0</v>
       </c>
       <c r="F2">
-        <v>0.08076355020774202</v>
+        <v>0.08108602682111143</v>
       </c>
       <c r="G2">
-        <v>7.689859368919306</v>
+        <v>7.742054073777023</v>
       </c>
       <c r="H2">
-        <v>1.4654943925052066e-14</v>
+        <v>9.769962616701378e-15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,22 +521,22 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-2.9352722367064845</v>
+        <v>-2.9325467960600102</v>
       </c>
       <c r="C3">
-        <v>0.08431663236081081</v>
+        <v>0.08433405292290803</v>
       </c>
       <c r="D3">
-        <v>-34.81249374554904</v>
+        <v>-34.77298545986789</v>
       </c>
       <c r="E3">
         <v>0.0</v>
       </c>
       <c r="F3">
-        <v>0.09068162916652442</v>
+        <v>0.09118145126916054</v>
       </c>
       <c r="G3">
-        <v>-32.36898436524842</v>
+        <v>-32.16165958362914</v>
       </c>
       <c r="H3">
         <v>0.0</v>
@@ -547,25 +547,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-1.0381289753399516</v>
+        <v>-1.0228161950026404</v>
       </c>
       <c r="C4">
-        <v>0.1341120478157573</v>
+        <v>0.1410587864878818</v>
       </c>
       <c r="D4">
-        <v>-7.740758509378142</v>
+        <v>-7.250992444136115</v>
       </c>
       <c r="E4">
-        <v>9.992007221626409e-15</v>
+        <v>4.1366909897533333e-13</v>
       </c>
       <c r="F4">
-        <v>0.16872227650665184</v>
+        <v>0.18614071211587616</v>
       </c>
       <c r="G4">
-        <v>-6.152886250909634</v>
+        <v>-5.494854851344491</v>
       </c>
       <c r="H4">
-        <v>7.608538243886187e-10</v>
+        <v>3.9103189797273785e-8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -573,22 +573,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-1.983810624459223</v>
+        <v>-1.9850271374948762</v>
       </c>
       <c r="C5">
-        <v>0.08977361437416424</v>
+        <v>0.08773953306823361</v>
       </c>
       <c r="D5">
-        <v>-22.097925301202306</v>
+        <v>-22.624090510615698</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.11722004546604478</v>
+        <v>0.11567313293314155</v>
       </c>
       <c r="G5">
-        <v>-16.923817224024837</v>
+        <v>-17.16065854844799</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -599,22 +599,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.8121109971613973</v>
+        <v>0.8456411273038463</v>
       </c>
       <c r="C6">
-        <v>0.09510660178405497</v>
+        <v>0.09425008915151031</v>
       </c>
       <c r="D6">
-        <v>8.538955045469317</v>
+        <v>8.972311166140635</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.09742719980278218</v>
+        <v>0.0974211533468297</v>
       </c>
       <c r="G6">
-        <v>8.335567467866467</v>
+        <v>8.680261916970677</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -625,25 +625,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.8098786901129168</v>
+        <v>0.8045875820068124</v>
       </c>
       <c r="C7">
-        <v>0.10754551860020954</v>
+        <v>0.0867173305975209</v>
       </c>
       <c r="D7">
-        <v>7.530566597791633</v>
+        <v>9.278278937587755</v>
       </c>
       <c r="E7">
-        <v>5.062616992290714e-14</v>
+        <v>0.0</v>
       </c>
       <c r="F7">
-        <v>0.11201067764352933</v>
+        <v>0.07863068259689669</v>
       </c>
       <c r="G7">
-        <v>7.230370417812593</v>
+        <v>10.232488838123947</v>
       </c>
       <c r="H7">
-        <v>4.816147480823929e-13</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -651,22 +651,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>0.9877123870805845</v>
+        <v>1.0031914554601777</v>
       </c>
       <c r="C8">
-        <v>0.0920902875013145</v>
+        <v>0.10313400834347587</v>
       </c>
       <c r="D8">
-        <v>10.725478374323524</v>
+        <v>9.727067449169287</v>
       </c>
       <c r="E8">
         <v>0.0</v>
       </c>
       <c r="F8">
-        <v>0.08969610991637915</v>
+        <v>0.11222395905955625</v>
       </c>
       <c r="G8">
-        <v>11.011763921550195</v>
+        <v>8.93919145133521</v>
       </c>
       <c r="H8">
         <v>0.0</v>
@@ -677,25 +677,25 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0.46859587521562457</v>
+        <v>0.4740185640328744</v>
       </c>
       <c r="C9">
-        <v>0.07064019073070321</v>
+        <v>0.0635154832005788</v>
       </c>
       <c r="D9">
-        <v>6.633559031600307</v>
+        <v>7.463039563691059</v>
       </c>
       <c r="E9">
-        <v>3.2768676661021345e-11</v>
+        <v>8.459899447643693e-14</v>
       </c>
       <c r="F9">
-        <v>0.061265948703940434</v>
+        <v>0.05407588560091</v>
       </c>
       <c r="G9">
-        <v>7.648553317603094</v>
+        <v>8.765803070359656</v>
       </c>
       <c r="H9">
-        <v>2.042810365310288e-14</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +713,7 @@
         <v>16</v>
       </c>
       <c r="B1">
-        <v>-1444.5644252262896</v>
+        <v>-1442.5013509009254</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -729,7 +729,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>7.4570910930633545</v>
+        <v>7.280930995941162</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -777,7 +777,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>2905.128850452579</v>
+        <v>2901.002701801851</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -785,7 +785,7 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>2954.394689788255</v>
+        <v>2950.268541137527</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -793,7 +793,7 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>0.40318845002330816</v>
+        <v>0.40404079455314446</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_routeChoice_lognormal.xlsx
+++ b/examples/output/MXL_routeChoice_lognormal.xlsx
@@ -753,7 +753,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>7.280930995941162</v>
+        <v>7.20083212852478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
